--- a/backend/excel/followups.xlsx
+++ b/backend/excel/followups.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,48 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>2026-10-07 16:28:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fup_af9e1ebed0fa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lead_2f8d3eba4432</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Call</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>emp_3dbe82c7aa1d</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:54:20</t>
         </is>
       </c>
     </row>

--- a/backend/excel/followups.xlsx
+++ b/backend/excel/followups.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,48 +455,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>created_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>fup_411bbf3dd29a</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>lead_40d2ac2ba106</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Call</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>okay for this project</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>emp_3dbe82c7aa1d</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-10-07 16:28:26</t>
         </is>
       </c>
     </row>
